--- a/Data/Output/mountains_enriched.xlsx
+++ b/Data/Output/mountains_enriched.xlsx
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/mountains_enriched.xlsx
+++ b/Data/Output/mountains_enriched.xlsx
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7756</v>
+        <v>8091</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="4"/>
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1691,11 +1691,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «K2» описує кілька об'єктів, узято найвідоміший; інші варіанти: 3253 (Q872294)</t>
+          <t>[wikidata_lookup] Назва «K2» неоднозначна; інші кандидати: 3253 (Q872294); підтверджено через llm_knowledge</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>2657</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2075,7 +2075,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7756</v>
+        <v>8091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>http://www.wikidata.org/entity/Q159621</t>
+          <t>http://www.wikidata.org/entity/Q16466024</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/mountains_enriched.xlsx
+++ b/Data/Output/mountains_enriched.xlsx
@@ -1611,7 +1611,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2657</v>
+        <v>1529</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>meters</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/mountains_enriched.xlsx
+++ b/Data/Output/mountains_enriched.xlsx
@@ -1643,7 +1643,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1524</v>
+        <v>3108</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/mountains_enriched.xlsx
+++ b/Data/Output/mountains_enriched.xlsx
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>3108</v>
+        <v>4513</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>

--- a/Data/Output/mountains_enriched.xlsx
+++ b/Data/Output/mountains_enriched.xlsx
@@ -1520,20 +1520,6 @@
   </sheetPr>
   <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="4" min="1" max="1"/>
-    <col width="16" customWidth="1" style="4" min="2" max="2"/>
-    <col width="12" customWidth="1" style="4" min="3" max="3"/>
-    <col width="8" customWidth="1" style="4" min="4" max="4"/>
-    <col width="20" customWidth="1" style="4" min="5" max="5"/>
-    <col width="46" customWidth="1" style="4" min="6" max="6"/>
-    <col width="40" customWidth="1" style="4" min="7" max="7"/>
-    <col width="8" customWidth="1" style="4" min="8" max="8"/>
-    <col width="14" customWidth="1" style="4" min="9" max="9"/>
-    <col width="60" customWidth="1" style="4" min="10" max="10"/>
-    <col width="12" customWidth="1" style="4" min="11" max="11"/>
-    <col width="10" customWidth="1" style="4" min="12" max="12"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
@@ -1643,7 +1629,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -1691,11 +1677,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[wikidata_lookup] Назва «K2» неоднозначна; інші кандидати: 3253 (Q872294); підтверджено через llm_knowledge</t>
+          <t>[wikidata_lookup] Назва «K2» неоднозначна; підтверджено llm_knowledge</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4513</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1747,7 +1733,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1799,7 +1785,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1851,7 +1837,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,7 +1889,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1955,7 +1941,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2007,7 +1993,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2059,7 +2045,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2111,7 +2097,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
